--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig2_monthly_heatmap_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig2_monthly_heatmap_data.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -509,31 +509,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.376506399515854</v>
+        <v>4.407141698173206</v>
       </c>
       <c r="C2" t="n">
-        <v>4.443404782056628</v>
+        <v>4.470137194908153</v>
       </c>
       <c r="D2" t="n">
-        <v>4.45676763303738</v>
+        <v>4.478709530253639</v>
       </c>
       <c r="E2" t="n">
-        <v>4.554023324229912</v>
+        <v>4.612952934526553</v>
       </c>
       <c r="F2" t="n">
-        <v>4.495699504265406</v>
+        <v>4.560789334852831</v>
       </c>
       <c r="G2" t="n">
-        <v>4.522989234066865</v>
+        <v>4.627037355572362</v>
       </c>
       <c r="H2" t="n">
-        <v>4.588555472955825</v>
+        <v>4.678490435916953</v>
       </c>
       <c r="I2" t="n">
-        <v>4.583883773612982</v>
+        <v>4.661098674428184</v>
       </c>
       <c r="J2" t="n">
-        <v>4.530734671516492</v>
+        <v>4.62055764449826</v>
       </c>
     </row>
     <row r="3">
@@ -543,31 +543,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.385583947716741</v>
+        <v>4.58534425297266</v>
       </c>
       <c r="C3" t="n">
-        <v>4.277711026074534</v>
+        <v>4.584159183357404</v>
       </c>
       <c r="D3" t="n">
-        <v>3.762217377260345</v>
+        <v>4.034634853781843</v>
       </c>
       <c r="E3" t="n">
-        <v>3.99176423023696</v>
+        <v>4.256395032188998</v>
       </c>
       <c r="F3" t="n">
-        <v>4.089578268549991</v>
+        <v>4.436927786706682</v>
       </c>
       <c r="G3" t="n">
-        <v>4.165407183082328</v>
+        <v>4.413377685831732</v>
       </c>
       <c r="H3" t="n">
-        <v>4.045060017367447</v>
+        <v>4.387565903611216</v>
       </c>
       <c r="I3" t="n">
-        <v>4.195000334710486</v>
+        <v>4.475716709219831</v>
       </c>
       <c r="J3" t="n">
-        <v>4.21525284794676</v>
+        <v>4.568167705199546</v>
       </c>
     </row>
     <row r="4">
@@ -577,31 +577,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.357371674750112</v>
+        <v>4.590725344699519</v>
       </c>
       <c r="C4" t="n">
-        <v>4.245970273205552</v>
+        <v>4.530597532962178</v>
       </c>
       <c r="D4" t="n">
-        <v>4.095371905436559</v>
+        <v>4.382295396955369</v>
       </c>
       <c r="E4" t="n">
-        <v>3.970600434136022</v>
+        <v>4.260938859824939</v>
       </c>
       <c r="F4" t="n">
-        <v>4.12788287666395</v>
+        <v>4.403073632670195</v>
       </c>
       <c r="G4" t="n">
-        <v>4.055279562402556</v>
+        <v>4.359524175152822</v>
       </c>
       <c r="H4" t="n">
-        <v>3.989925553237625</v>
+        <v>4.251704542718411</v>
       </c>
       <c r="I4" t="n">
-        <v>4.205982655156188</v>
+        <v>4.42320685302688</v>
       </c>
       <c r="J4" t="n">
-        <v>4.056712417311156</v>
+        <v>4.31930305293242</v>
       </c>
     </row>
     <row r="5">
@@ -611,31 +611,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.093284304792274</v>
+        <v>4.76876168523869</v>
       </c>
       <c r="C5" t="n">
-        <v>4.138618797888473</v>
+        <v>4.901873568081522</v>
       </c>
       <c r="D5" t="n">
-        <v>4.092101981508838</v>
+        <v>4.375781370101784</v>
       </c>
       <c r="E5" t="n">
-        <v>3.995228572304625</v>
+        <v>4.494883325312365</v>
       </c>
       <c r="F5" t="n">
-        <v>3.676723963681436</v>
+        <v>4.846149350422658</v>
       </c>
       <c r="G5" t="n">
-        <v>3.961073674800473</v>
+        <v>4.707249561712934</v>
       </c>
       <c r="H5" t="n">
-        <v>3.84592862353879</v>
+        <v>4.747157407743331</v>
       </c>
       <c r="I5" t="n">
-        <v>3.833144215123108</v>
+        <v>4.707126905533682</v>
       </c>
       <c r="J5" t="n">
-        <v>3.750275035599294</v>
+        <v>4.92985430724637</v>
       </c>
     </row>
     <row r="6">
@@ -645,31 +645,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.308993017615503</v>
+        <v>4.301598483919747</v>
       </c>
       <c r="C6" t="n">
-        <v>4.333190303009718</v>
+        <v>4.266535661110623</v>
       </c>
       <c r="D6" t="n">
-        <v>4.434471205110603</v>
+        <v>4.410326239546518</v>
       </c>
       <c r="E6" t="n">
-        <v>4.318539750721442</v>
+        <v>4.34088931207777</v>
       </c>
       <c r="F6" t="n">
-        <v>4.43293018538917</v>
+        <v>4.449267221591825</v>
       </c>
       <c r="G6" t="n">
-        <v>4.500700229029503</v>
+        <v>4.501286000026779</v>
       </c>
       <c r="H6" t="n">
-        <v>4.52707492580955</v>
+        <v>4.490742238950209</v>
       </c>
       <c r="I6" t="n">
-        <v>4.461935514931037</v>
+        <v>4.448428029984018</v>
       </c>
       <c r="J6" t="n">
-        <v>4.512432044632413</v>
+        <v>4.483435500862674</v>
       </c>
     </row>
     <row r="7">
@@ -679,31 +679,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.576043858609802</v>
+        <v>4.553617833296489</v>
       </c>
       <c r="C7" t="n">
-        <v>4.499768971438489</v>
+        <v>4.347555696500602</v>
       </c>
       <c r="D7" t="n">
-        <v>4.481716380804502</v>
+        <v>4.387686268228872</v>
       </c>
       <c r="E7" t="n">
-        <v>4.382862722352521</v>
+        <v>4.340220211162373</v>
       </c>
       <c r="F7" t="n">
-        <v>4.381473898071697</v>
+        <v>4.292303089834899</v>
       </c>
       <c r="G7" t="n">
-        <v>4.526738705869431</v>
+        <v>4.416932306392916</v>
       </c>
       <c r="H7" t="n">
-        <v>4.529479205314958</v>
+        <v>4.373771950689251</v>
       </c>
       <c r="I7" t="n">
-        <v>4.483819559566378</v>
+        <v>4.419163112229175</v>
       </c>
       <c r="J7" t="n">
-        <v>4.536560527399148</v>
+        <v>4.462788978466537</v>
       </c>
     </row>
     <row r="8">
@@ -713,31 +713,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.266466621596718</v>
+        <v>4.580697141158795</v>
       </c>
       <c r="C8" t="n">
-        <v>3.644342673022326</v>
+        <v>3.332803926548602</v>
       </c>
       <c r="D8" t="n">
-        <v>3.837654276022439</v>
+        <v>3.719747376655706</v>
       </c>
       <c r="E8" t="n">
-        <v>4.152353302044409</v>
+        <v>4.306938263082275</v>
       </c>
       <c r="F8" t="n">
-        <v>3.9299543630293</v>
+        <v>3.956868392653828</v>
       </c>
       <c r="G8" t="n">
-        <v>3.992865998314149</v>
+        <v>4.0211581365017</v>
       </c>
       <c r="H8" t="n">
-        <v>3.813009575808064</v>
+        <v>3.851942577283802</v>
       </c>
       <c r="I8" t="n">
-        <v>3.737794743348421</v>
+        <v>3.827383823445346</v>
       </c>
       <c r="J8" t="n">
-        <v>3.93394674431416</v>
+        <v>4.008083893292857</v>
       </c>
     </row>
     <row r="9">
@@ -747,31 +747,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.978108912923699</v>
+        <v>4.112461005228921</v>
       </c>
       <c r="C9" t="n">
-        <v>3.770109741378511</v>
+        <v>3.89695553302593</v>
       </c>
       <c r="D9" t="n">
-        <v>3.870469787593179</v>
+        <v>3.995665065262146</v>
       </c>
       <c r="E9" t="n">
-        <v>3.84220878049164</v>
+        <v>4.058515192745756</v>
       </c>
       <c r="F9" t="n">
-        <v>3.663864200715266</v>
+        <v>3.845760408643478</v>
       </c>
       <c r="G9" t="n">
-        <v>3.636358870204619</v>
+        <v>3.83966611438174</v>
       </c>
       <c r="H9" t="n">
-        <v>3.459581350457263</v>
+        <v>3.645804026992299</v>
       </c>
       <c r="I9" t="n">
-        <v>3.611438537724408</v>
+        <v>3.902713009505651</v>
       </c>
       <c r="J9" t="n">
-        <v>3.57407006776118</v>
+        <v>3.758642950576733</v>
       </c>
     </row>
     <row r="10">
@@ -781,31 +781,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.393835889781006</v>
+        <v>4.468214106342947</v>
       </c>
       <c r="C10" t="n">
-        <v>4.257799891943981</v>
+        <v>4.277966762852764</v>
       </c>
       <c r="D10" t="n">
-        <v>4.212392377438281</v>
+        <v>4.106497407810968</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2381974056442</v>
+        <v>4.165838575777559</v>
       </c>
       <c r="F10" t="n">
-        <v>4.23313880359068</v>
+        <v>4.174040393248138</v>
       </c>
       <c r="G10" t="n">
-        <v>4.119279393146329</v>
+        <v>4.00328773868929</v>
       </c>
       <c r="H10" t="n">
-        <v>3.985064209981642</v>
+        <v>3.81020774731109</v>
       </c>
       <c r="I10" t="n">
-        <v>4.097790943941255</v>
+        <v>3.894616131717093</v>
       </c>
       <c r="J10" t="n">
-        <v>4.091925488659779</v>
+        <v>3.906214350761737</v>
       </c>
     </row>
     <row r="11">
@@ -815,31 +815,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.231563850909132</v>
+        <v>4.344578600778806</v>
       </c>
       <c r="C11" t="n">
-        <v>4.088517073038615</v>
+        <v>4.152870096189541</v>
       </c>
       <c r="D11" t="n">
-        <v>4.183515881443967</v>
+        <v>4.287822912705866</v>
       </c>
       <c r="E11" t="n">
-        <v>4.185887718110032</v>
+        <v>4.334388298345646</v>
       </c>
       <c r="F11" t="n">
-        <v>3.720498929960765</v>
+        <v>3.718029484553087</v>
       </c>
       <c r="G11" t="n">
-        <v>3.203438274681529</v>
+        <v>3.186374530180101</v>
       </c>
       <c r="H11" t="n">
-        <v>3.234037622619021</v>
+        <v>3.186953771262435</v>
       </c>
       <c r="I11" t="n">
-        <v>3.501721104163146</v>
+        <v>3.560338091523808</v>
       </c>
       <c r="J11" t="n">
-        <v>3.113758135998652</v>
+        <v>3.189585069301626</v>
       </c>
     </row>
     <row r="12">
@@ -849,31 +849,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.89781523798774</v>
+        <v>4.146070653849239</v>
       </c>
       <c r="C12" t="n">
-        <v>3.892934868183927</v>
+        <v>4.080962978022485</v>
       </c>
       <c r="D12" t="n">
-        <v>3.554269708452653</v>
+        <v>3.789260932397677</v>
       </c>
       <c r="E12" t="n">
-        <v>3.944636287099085</v>
+        <v>4.210116826645573</v>
       </c>
       <c r="F12" t="n">
-        <v>3.820136519267297</v>
+        <v>4.163037751017944</v>
       </c>
       <c r="G12" t="n">
-        <v>3.786782547570148</v>
+        <v>4.057027887037345</v>
       </c>
       <c r="H12" t="n">
-        <v>3.964630358254439</v>
+        <v>4.248826313959218</v>
       </c>
       <c r="I12" t="n">
-        <v>3.909156580110705</v>
+        <v>4.166424243897086</v>
       </c>
       <c r="J12" t="n">
-        <v>4.014520627665988</v>
+        <v>4.273649512345282</v>
       </c>
     </row>
     <row r="13">
@@ -883,31 +883,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.365213977159812</v>
+        <v>4.479718760696324</v>
       </c>
       <c r="C13" t="n">
-        <v>4.214359329247626</v>
+        <v>4.27866743334289</v>
       </c>
       <c r="D13" t="n">
-        <v>4.09217051941059</v>
+        <v>4.133384621837962</v>
       </c>
       <c r="E13" t="n">
-        <v>4.040671427733117</v>
+        <v>4.0515620540473</v>
       </c>
       <c r="F13" t="n">
-        <v>4.097052653831886</v>
+        <v>4.31724232734915</v>
       </c>
       <c r="G13" t="n">
-        <v>4.268094292376325</v>
+        <v>4.409186684209421</v>
       </c>
       <c r="H13" t="n">
-        <v>4.180994771611436</v>
+        <v>4.239579000233142</v>
       </c>
       <c r="I13" t="n">
-        <v>4.164871492449802</v>
+        <v>4.22748026333662</v>
       </c>
       <c r="J13" t="n">
-        <v>4.180356790877382</v>
+        <v>4.223447409655141</v>
       </c>
     </row>
     <row r="14">
@@ -917,31 +917,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.301212999547493</v>
+        <v>4.424403218606899</v>
       </c>
       <c r="C14" t="n">
-        <v>4.180999456793435</v>
+        <v>4.320731594458209</v>
       </c>
       <c r="D14" t="n">
-        <v>4.220445658761351</v>
+        <v>4.370641106844363</v>
       </c>
       <c r="E14" t="n">
-        <v>4.236341064149624</v>
+        <v>4.349454946319307</v>
       </c>
       <c r="F14" t="n">
-        <v>4.112927538703701</v>
+        <v>4.088436927462847</v>
       </c>
       <c r="G14" t="n">
-        <v>4.056527825071717</v>
+        <v>4.072319720241801</v>
       </c>
       <c r="H14" t="n">
-        <v>3.957091768481676</v>
+        <v>4.008110293915871</v>
       </c>
       <c r="I14" t="n">
-        <v>4.044259400546268</v>
+        <v>3.995198185869864</v>
       </c>
       <c r="J14" t="n">
-        <v>3.408378397433343</v>
+        <v>3.442151795724789</v>
       </c>
     </row>
     <row r="15">
@@ -951,31 +951,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.06567689733073</v>
+        <v>4.197547613347384</v>
       </c>
       <c r="C15" t="n">
-        <v>4.120444818277811</v>
+        <v>4.239880570545794</v>
       </c>
       <c r="D15" t="n">
-        <v>4.091701716060071</v>
+        <v>4.242036783915132</v>
       </c>
       <c r="E15" t="n">
-        <v>4.03851296904835</v>
+        <v>4.150036781750293</v>
       </c>
       <c r="F15" t="n">
-        <v>4.067287825755254</v>
+        <v>4.186780041130376</v>
       </c>
       <c r="G15" t="n">
-        <v>4.024664535207395</v>
+        <v>4.190596462824255</v>
       </c>
       <c r="H15" t="n">
-        <v>4.094138463154668</v>
+        <v>4.237187157259488</v>
       </c>
       <c r="I15" t="n">
-        <v>4.127408952672909</v>
+        <v>4.266397404754463</v>
       </c>
       <c r="J15" t="n">
-        <v>3.913939755438086</v>
+        <v>4.070666009247597</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig2_monthly_heatmap_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig2_monthly_heatmap_data.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -509,31 +509,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.407141698173206</v>
+        <v>4.407026974798561</v>
       </c>
       <c r="C2" t="n">
-        <v>4.470137194908153</v>
+        <v>4.469009081033353</v>
       </c>
       <c r="D2" t="n">
-        <v>4.478709530253639</v>
+        <v>4.479596945458823</v>
       </c>
       <c r="E2" t="n">
-        <v>4.612952934526553</v>
+        <v>4.6157643245701</v>
       </c>
       <c r="F2" t="n">
-        <v>4.560789334852831</v>
+        <v>4.56171044758674</v>
       </c>
       <c r="G2" t="n">
-        <v>4.627037355572362</v>
+        <v>4.627928536290468</v>
       </c>
       <c r="H2" t="n">
-        <v>4.678490435916953</v>
+        <v>4.678887685403278</v>
       </c>
       <c r="I2" t="n">
-        <v>4.661098674428184</v>
+        <v>4.662152223102444</v>
       </c>
       <c r="J2" t="n">
-        <v>4.62055764449826</v>
+        <v>4.620792865624042</v>
       </c>
     </row>
     <row r="3">
@@ -747,31 +747,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.112461005228921</v>
+        <v>4.116708582671366</v>
       </c>
       <c r="C9" t="n">
-        <v>3.89695553302593</v>
+        <v>3.854025806254701</v>
       </c>
       <c r="D9" t="n">
-        <v>3.995665065262146</v>
+        <v>3.992595274114745</v>
       </c>
       <c r="E9" t="n">
-        <v>4.058515192745756</v>
+        <v>4.035619914224371</v>
       </c>
       <c r="F9" t="n">
-        <v>3.845760408643478</v>
+        <v>3.781964711446813</v>
       </c>
       <c r="G9" t="n">
-        <v>3.83966611438174</v>
+        <v>3.746749726500814</v>
       </c>
       <c r="H9" t="n">
-        <v>3.645804026992299</v>
+        <v>3.492445313854469</v>
       </c>
       <c r="I9" t="n">
-        <v>3.902713009505651</v>
+        <v>3.759303468291522</v>
       </c>
       <c r="J9" t="n">
-        <v>3.758642950576733</v>
+        <v>3.661425813386364</v>
       </c>
     </row>
     <row r="10">
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.344578600778806</v>
+        <v>4.344975376991987</v>
       </c>
       <c r="C11" t="n">
-        <v>4.152870096189541</v>
+        <v>4.145044667903421</v>
       </c>
       <c r="D11" t="n">
-        <v>4.287822912705866</v>
+        <v>4.274998318024101</v>
       </c>
       <c r="E11" t="n">
-        <v>4.334388298345646</v>
+        <v>4.325639101024967</v>
       </c>
       <c r="F11" t="n">
-        <v>3.718029484553087</v>
+        <v>3.726958152753968</v>
       </c>
       <c r="G11" t="n">
-        <v>3.186374530180101</v>
+        <v>3.184510380332858</v>
       </c>
       <c r="H11" t="n">
-        <v>3.186953771262435</v>
+        <v>3.188701016186656</v>
       </c>
       <c r="I11" t="n">
         <v>3.560338091523808</v>
@@ -883,31 +883,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.479718760696324</v>
+        <v>4.478897919515331</v>
       </c>
       <c r="C13" t="n">
-        <v>4.27866743334289</v>
+        <v>4.277818676493171</v>
       </c>
       <c r="D13" t="n">
-        <v>4.133384621837962</v>
+        <v>4.13082415775377</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0515620540473</v>
+        <v>4.04951955271255</v>
       </c>
       <c r="F13" t="n">
-        <v>4.31724232734915</v>
+        <v>4.321774084983277</v>
       </c>
       <c r="G13" t="n">
-        <v>4.409186684209421</v>
+        <v>4.444273911771564</v>
       </c>
       <c r="H13" t="n">
-        <v>4.239579000233142</v>
+        <v>4.344453169265362</v>
       </c>
       <c r="I13" t="n">
-        <v>4.22748026333662</v>
+        <v>4.329435755037346</v>
       </c>
       <c r="J13" t="n">
-        <v>4.223447409655141</v>
+        <v>4.308278317976778</v>
       </c>
     </row>
     <row r="14">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig2_monthly_heatmap_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig2_monthly_heatmap_data.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-8fdd3599890f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -747,31 +747,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.116708582671366</v>
+        <v>4.114688743770995</v>
       </c>
       <c r="C9" t="n">
-        <v>3.854025806254701</v>
+        <v>3.923349461727971</v>
       </c>
       <c r="D9" t="n">
-        <v>3.992595274114745</v>
+        <v>4.051016745751208</v>
       </c>
       <c r="E9" t="n">
-        <v>4.035619914224371</v>
+        <v>4.064109649337524</v>
       </c>
       <c r="F9" t="n">
-        <v>3.781964711446813</v>
+        <v>3.827340161626869</v>
       </c>
       <c r="G9" t="n">
-        <v>3.746749726500814</v>
+        <v>3.807664079734292</v>
       </c>
       <c r="H9" t="n">
-        <v>3.492445313854469</v>
+        <v>3.583846434120448</v>
       </c>
       <c r="I9" t="n">
-        <v>3.759303468291522</v>
+        <v>3.839049377525943</v>
       </c>
       <c r="J9" t="n">
-        <v>3.661425813386364</v>
+        <v>3.72646458672447</v>
       </c>
     </row>
     <row r="10">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig2_monthly_heatmap_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig2_monthly_heatmap_data.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
